--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N22_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.81469273405759</v>
+        <v>1.919887569284358</v>
       </c>
       <c r="D2" t="n">
-        <v>9.421402682749266</v>
+        <v>1.530977935946756</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
